--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251001_170359.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251001_170359.xlsx
@@ -9000,7 +9000,7 @@
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -9124,7 +9124,7 @@
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -9186,7 +9186,7 @@
       </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251001_170359.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251001_170359.xlsx
@@ -9000,7 +9000,7 @@
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -9124,7 +9124,7 @@
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -9186,7 +9186,7 @@
       </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -11480,7 +11480,7 @@
       </c>
       <c r="P178" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -11542,7 +11542,7 @@
       </c>
       <c r="P179" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -12038,7 +12038,7 @@
       </c>
       <c r="P187" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251001_170359.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251001_170359.xlsx
@@ -11604,7 +11604,7 @@
       </c>
       <c r="P180" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251001_170359.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251001_170359.xlsx
@@ -11480,7 +11480,7 @@
       </c>
       <c r="P178" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -11542,7 +11542,7 @@
       </c>
       <c r="P179" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -12038,7 +12038,7 @@
       </c>
       <c r="P187" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251001_170359.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251001_170359.xlsx
@@ -11604,7 +11604,7 @@
       </c>
       <c r="P180" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251001_170359.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251001_170359.xlsx
@@ -11480,7 +11480,7 @@
       </c>
       <c r="P178" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -11542,7 +11542,7 @@
       </c>
       <c r="P179" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -11604,7 +11604,7 @@
       </c>
       <c r="P180" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -12038,7 +12038,7 @@
       </c>
       <c r="P187" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251001_170359.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251001_170359.xlsx
@@ -11480,7 +11480,7 @@
       </c>
       <c r="P178" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -11542,7 +11542,7 @@
       </c>
       <c r="P179" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -11604,7 +11604,7 @@
       </c>
       <c r="P180" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -12038,7 +12038,7 @@
       </c>
       <c r="P187" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251001_170359.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251001_170359.xlsx
@@ -9000,7 +9000,7 @@
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -9124,7 +9124,7 @@
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -9186,7 +9186,7 @@
       </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251001_170359.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251001_170359.xlsx
@@ -9000,7 +9000,7 @@
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -9124,7 +9124,7 @@
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -9186,7 +9186,7 @@
       </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -11604,7 +11604,7 @@
       </c>
       <c r="P180" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251001_170359.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251001_170359.xlsx
@@ -11480,7 +11480,7 @@
       </c>
       <c r="P178" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -11542,7 +11542,7 @@
       </c>
       <c r="P179" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -12038,7 +12038,7 @@
       </c>
       <c r="P187" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251001_170359.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251001_170359.xlsx
@@ -9000,7 +9000,7 @@
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -9124,7 +9124,7 @@
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -9186,7 +9186,7 @@
       </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -11480,7 +11480,7 @@
       </c>
       <c r="P178" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -11542,7 +11542,7 @@
       </c>
       <c r="P179" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -12038,7 +12038,7 @@
       </c>
       <c r="P187" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251001_170359.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251001_170359.xlsx
@@ -9000,7 +9000,7 @@
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -9124,7 +9124,7 @@
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -9186,7 +9186,7 @@
       </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -11480,7 +11480,7 @@
       </c>
       <c r="P178" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -11542,7 +11542,7 @@
       </c>
       <c r="P179" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -11604,7 +11604,7 @@
       </c>
       <c r="P180" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -12038,7 +12038,7 @@
       </c>
       <c r="P187" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251001_170359.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251001_170359.xlsx
@@ -11480,7 +11480,7 @@
       </c>
       <c r="P178" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -11542,7 +11542,7 @@
       </c>
       <c r="P179" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -11604,7 +11604,7 @@
       </c>
       <c r="P180" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -12038,7 +12038,7 @@
       </c>
       <c r="P187" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251001_170359.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petlove_20251001_170359.xlsx
@@ -9000,7 +9000,7 @@
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -9124,7 +9124,7 @@
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -9186,7 +9186,7 @@
       </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -11480,7 +11480,7 @@
       </c>
       <c r="P178" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -11542,7 +11542,7 @@
       </c>
       <c r="P179" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -12038,7 +12038,7 @@
       </c>
       <c r="P187" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
